--- a/sheets/조재수대금교본/검수/허공.xlsx
+++ b/sheets/조재수대금교본/검수/허공.xlsx
@@ -3415,29 +3415,13 @@
         </is>
       </c>
       <c r="C4" s="23"/>
-      <c r="D4" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Z</t>
-        </is>
-      </c>
+      <c r="D4" s="21"/>
       <c r="E4" s="23"/>
-      <c r="F4" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Z</t>
-        </is>
-      </c>
+      <c r="F4" s="21"/>
       <c r="G4" s="23"/>
-      <c r="H4" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Z</t>
-        </is>
-      </c>
+      <c r="H4" s="21"/>
       <c r="I4" s="23"/>
-      <c r="J4" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Z</t>
-        </is>
-      </c>
+      <c r="J4" s="21"/>
       <c r="K4" s="23"/>
       <c r="L4" s="21" t="inlineStr">
         <is>
@@ -3461,11 +3445,7 @@
     </row>
     <row r="5" ht="86.26" customHeight="true">
       <c r="A5" s="0"/>
-      <c r="B5" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="B5" s="21"/>
       <c r="C5" s="24"/>
       <c r="D5" s="21" t="inlineStr">
         <is>
@@ -3483,8 +3463,7 @@
       <c r="G5" s="24"/>
       <c r="H5" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–
-Z</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I5" s="24"/>
@@ -3497,8 +3476,7 @@
       <c r="K5" s="24"/>
       <c r="L5" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–
-Z</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="M5" s="24"/>
@@ -3553,11 +3531,7 @@
         </is>
       </c>
       <c r="K6" s="22"/>
-      <c r="L6" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Z</t>
-        </is>
-      </c>
+      <c r="L6" s="21"/>
       <c r="M6" s="22"/>
       <c r="N6" s="21" t="inlineStr">
         <is>
@@ -3581,11 +3555,7 @@
         </is>
       </c>
       <c r="C7" s="23"/>
-      <c r="D7" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Z</t>
-        </is>
-      </c>
+      <c r="D7" s="21"/>
       <c r="E7" s="23"/>
       <c r="F7" s="21" t="inlineStr">
         <is>
@@ -3594,17 +3564,9 @@
         </is>
       </c>
       <c r="G7" s="23"/>
-      <c r="H7" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Z</t>
-        </is>
-      </c>
+      <c r="H7" s="21"/>
       <c r="I7" s="23"/>
-      <c r="J7" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Z</t>
-        </is>
-      </c>
+      <c r="J7" s="21"/>
       <c r="K7" s="23"/>
       <c r="L7" s="21"/>
       <c r="M7" s="23"/>
@@ -3622,24 +3584,15 @@
         </is>
       </c>
       <c r="C8" s="24"/>
-      <c r="D8" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="D8" s="21"/>
       <c r="E8" s="24"/>
       <c r="F8" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">南
-‹</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="G8" s="24"/>
-      <c r="H8" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="H8" s="21"/>
       <c r="I8" s="24"/>
       <c r="J8" s="21" t="inlineStr">
         <is>
@@ -3648,11 +3601,7 @@
         </is>
       </c>
       <c r="K8" s="24"/>
-      <c r="L8" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="L8" s="21"/>
       <c r="M8" s="24"/>
       <c r="N8" s="21" t="inlineStr">
         <is>
@@ -3661,11 +3610,7 @@
         </is>
       </c>
       <c r="O8" s="24"/>
-      <c r="P8" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="P8" s="21"/>
       <c r="Q8" s="24"/>
     </row>
     <row r="9" ht="86.26" customHeight="true">
@@ -3771,8 +3716,7 @@
       <c r="C11" s="24"/>
       <c r="D11" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–
-Z</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="E11" s="24"/>
@@ -3803,8 +3747,7 @@
       <c r="O11" s="24"/>
       <c r="P11" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">c
-仲</t>
+          <t xml:space="preserve">仲</t>
         </is>
       </c>
       <c r="Q11" s="24"/>
@@ -3828,7 +3771,7 @@
       <c r="G12" s="22"/>
       <c r="H12" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">淋∽</t>
+          <t xml:space="preserve">淋</t>
         </is>
       </c>
       <c r="I12" s="22"/>
@@ -3881,47 +3824,19 @@
         </is>
       </c>
       <c r="C14" s="24"/>
-      <c r="D14" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="D14" s="21"/>
       <c r="E14" s="24"/>
-      <c r="F14" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="F14" s="21"/>
       <c r="G14" s="24"/>
-      <c r="H14" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="H14" s="21"/>
       <c r="I14" s="24"/>
-      <c r="J14" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="J14" s="21"/>
       <c r="K14" s="24"/>
-      <c r="L14" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="L14" s="21"/>
       <c r="M14" s="24"/>
-      <c r="N14" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="N14" s="21"/>
       <c r="O14" s="24"/>
-      <c r="P14" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="P14" s="21"/>
       <c r="Q14" s="24"/>
     </row>
   </sheetData>

--- a/sheets/조재수대금교본/검수/허공.xlsx
+++ b/sheets/조재수대금교본/검수/허공.xlsx
@@ -3415,13 +3415,29 @@
         </is>
       </c>
       <c r="C4" s="23"/>
-      <c r="D4" s="21"/>
+      <c r="D4" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Z</t>
+        </is>
+      </c>
       <c r="E4" s="23"/>
-      <c r="F4" s="21"/>
+      <c r="F4" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Z</t>
+        </is>
+      </c>
       <c r="G4" s="23"/>
-      <c r="H4" s="21"/>
+      <c r="H4" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Z</t>
+        </is>
+      </c>
       <c r="I4" s="23"/>
-      <c r="J4" s="21"/>
+      <c r="J4" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Z</t>
+        </is>
+      </c>
       <c r="K4" s="23"/>
       <c r="L4" s="21" t="inlineStr">
         <is>
@@ -3463,7 +3479,8 @@
       <c r="G5" s="24"/>
       <c r="H5" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–</t>
+          <t xml:space="preserve">–
+Z</t>
         </is>
       </c>
       <c r="I5" s="24"/>
@@ -3476,7 +3493,8 @@
       <c r="K5" s="24"/>
       <c r="L5" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–</t>
+          <t xml:space="preserve">–
+Z</t>
         </is>
       </c>
       <c r="M5" s="24"/>
@@ -3531,7 +3549,11 @@
         </is>
       </c>
       <c r="K6" s="22"/>
-      <c r="L6" s="21"/>
+      <c r="L6" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Z</t>
+        </is>
+      </c>
       <c r="M6" s="22"/>
       <c r="N6" s="21" t="inlineStr">
         <is>
@@ -3555,7 +3577,11 @@
         </is>
       </c>
       <c r="C7" s="23"/>
-      <c r="D7" s="21"/>
+      <c r="D7" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Z</t>
+        </is>
+      </c>
       <c r="E7" s="23"/>
       <c r="F7" s="21" t="inlineStr">
         <is>
@@ -3564,9 +3590,17 @@
         </is>
       </c>
       <c r="G7" s="23"/>
-      <c r="H7" s="21"/>
+      <c r="H7" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Z</t>
+        </is>
+      </c>
       <c r="I7" s="23"/>
-      <c r="J7" s="21"/>
+      <c r="J7" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Z</t>
+        </is>
+      </c>
       <c r="K7" s="23"/>
       <c r="L7" s="21"/>
       <c r="M7" s="23"/>
@@ -3716,7 +3750,8 @@
       <c r="C11" s="24"/>
       <c r="D11" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–</t>
+          <t xml:space="preserve">–
+Z</t>
         </is>
       </c>
       <c r="E11" s="24"/>
@@ -3747,7 +3782,8 @@
       <c r="O11" s="24"/>
       <c r="P11" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲</t>
+          <t xml:space="preserve">c
+仲</t>
         </is>
       </c>
       <c r="Q11" s="24"/>
@@ -3771,7 +3807,7 @@
       <c r="G12" s="22"/>
       <c r="H12" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">淋</t>
+          <t xml:space="preserve">淋∽</t>
         </is>
       </c>
       <c r="I12" s="22"/>

--- a/sheets/조재수대금교본/검수/허공.xlsx
+++ b/sheets/조재수대금교본/검수/허공.xlsx
@@ -3303,28 +3303,28 @@
   </sheetPr>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="10.71" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="10.71" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="10.71" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="10.71" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="9" customWidth="1"/>
+    <col min="10" max="10" width="10.71" customWidth="1"/>
     <col min="11" max="11" width="6" customWidth="1"/>
-    <col min="12" max="12" width="9" customWidth="1"/>
+    <col min="12" max="12" width="10.71" customWidth="1"/>
     <col min="13" max="13" width="6" customWidth="1"/>
-    <col min="14" max="14" width="9" customWidth="1"/>
+    <col min="14" max="14" width="10.71" customWidth="1"/>
     <col min="15" max="15" width="6" customWidth="1"/>
-    <col min="16" max="16" width="9" customWidth="1"/>
+    <col min="16" max="16" width="10.71" customWidth="1"/>
     <col min="17" max="17" width="6" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="6.0" customHeight="true">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="57.97" customHeight="true">
+    <row r="2" ht="64.52" customHeight="true">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -3347,7 +3347,7 @@
       <c r="P2" s="20"/>
       <c r="Q2" s="20"/>
     </row>
-    <row r="3" ht="86.26" customHeight="true">
+    <row r="3" ht="96.05" customHeight="true">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -3406,7 +3406,7 @@
       </c>
       <c r="Q3" s="22"/>
     </row>
-    <row r="4" ht="86.26" customHeight="true">
+    <row r="4" ht="96.05" customHeight="true">
       <c r="A4" s="0"/>
       <c r="B4" s="21" t="inlineStr">
         <is>
@@ -3459,7 +3459,7 @@
       </c>
       <c r="Q4" s="23"/>
     </row>
-    <row r="5" ht="86.26" customHeight="true">
+    <row r="5" ht="96.05" customHeight="true">
       <c r="A5" s="0"/>
       <c r="B5" s="21"/>
       <c r="C5" s="24"/>
@@ -3513,7 +3513,7 @@
       </c>
       <c r="Q5" s="24"/>
     </row>
-    <row r="6" ht="86.26" customHeight="true">
+    <row r="6" ht="96.05" customHeight="true">
       <c r="A6" s="0"/>
       <c r="B6" s="21" t="inlineStr">
         <is>
@@ -3568,7 +3568,7 @@
       </c>
       <c r="Q6" s="22"/>
     </row>
-    <row r="7" ht="86.26" customHeight="true">
+    <row r="7" ht="96.05" customHeight="true">
       <c r="A7" s="0"/>
       <c r="B7" s="21" t="inlineStr">
         <is>
@@ -3609,7 +3609,7 @@
       <c r="P7" s="21"/>
       <c r="Q7" s="23"/>
     </row>
-    <row r="8" ht="86.26" customHeight="true">
+    <row r="8" ht="96.05" customHeight="true">
       <c r="A8" s="0"/>
       <c r="B8" s="21" t="inlineStr">
         <is>
@@ -3647,7 +3647,7 @@
       <c r="P8" s="21"/>
       <c r="Q8" s="24"/>
     </row>
-    <row r="9" ht="86.26" customHeight="true">
+    <row r="9" ht="96.05" customHeight="true">
       <c r="A9" s="0"/>
       <c r="B9" s="21" t="inlineStr">
         <is>
@@ -3703,7 +3703,7 @@
       </c>
       <c r="Q9" s="22"/>
     </row>
-    <row r="10" ht="86.26" customHeight="true">
+    <row r="10" ht="96.05" customHeight="true">
       <c r="A10" s="0"/>
       <c r="B10" s="21"/>
       <c r="C10" s="23"/>
@@ -3744,7 +3744,7 @@
       </c>
       <c r="Q10" s="23"/>
     </row>
-    <row r="11" ht="86.26" customHeight="true">
+    <row r="11" ht="96.05" customHeight="true">
       <c r="A11" s="0"/>
       <c r="B11" s="21"/>
       <c r="C11" s="24"/>
@@ -3788,7 +3788,7 @@
       </c>
       <c r="Q11" s="24"/>
     </row>
-    <row r="12" ht="86.26" customHeight="true">
+    <row r="12" ht="96.05" customHeight="true">
       <c r="A12" s="0"/>
       <c r="B12" s="21"/>
       <c r="C12" s="22"/>
@@ -3828,7 +3828,7 @@
       </c>
       <c r="Q12" s="22"/>
     </row>
-    <row r="13" ht="86.26" customHeight="true">
+    <row r="13" ht="96.05" customHeight="true">
       <c r="A13" s="0"/>
       <c r="B13" s="21"/>
       <c r="C13" s="23"/>
@@ -3851,7 +3851,7 @@
       <c r="P13" s="21"/>
       <c r="Q13" s="23"/>
     </row>
-    <row r="14" ht="86.26" customHeight="true">
+    <row r="14" ht="96.05" customHeight="true">
       <c r="A14" s="0"/>
       <c r="B14" s="21" t="inlineStr">
         <is>
@@ -3881,6 +3881,6 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" scale="69"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="62"/>
 </worksheet>
 </file>